--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N100_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N100_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>64.14031227451851</v>
+        <v>10.42280074460926</v>
       </c>
       <c r="D2" t="n">
-        <v>45.91777752235162</v>
+        <v>7.461638847382138</v>
       </c>
       <c r="E2" t="n">
-        <v>8.302310750264049</v>
+        <v>1.349125496917908</v>
       </c>
       <c r="F2" t="n">
-        <v>9.274827542583708</v>
+        <v>1.507159475669853</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>74.19992809021979</v>
+        <v>12.05748831466072</v>
       </c>
       <c r="D3" t="n">
-        <v>72.10753379421887</v>
+        <v>11.71747424156057</v>
       </c>
       <c r="E3" t="n">
-        <v>8.302310750264049</v>
+        <v>1.349125496917908</v>
       </c>
       <c r="F3" t="n">
-        <v>9.274827542583708</v>
+        <v>1.507159475669853</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>58.58893021722829</v>
+        <v>9.520701160299597</v>
       </c>
       <c r="D4" t="n">
-        <v>56.77130064792372</v>
+        <v>9.225336355287606</v>
       </c>
       <c r="E4" t="n">
-        <v>8.302310750264049</v>
+        <v>1.349125496917908</v>
       </c>
       <c r="F4" t="n">
-        <v>9.274827542583708</v>
+        <v>1.507159475669853</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>67.05262122782878</v>
+        <v>10.89605094952218</v>
       </c>
       <c r="D5" t="n">
-        <v>66.69685714361961</v>
+        <v>10.83823928583819</v>
       </c>
       <c r="E5" t="n">
-        <v>8.302310750264049</v>
+        <v>1.349125496917908</v>
       </c>
       <c r="F5" t="n">
-        <v>9.274827542583708</v>
+        <v>1.507159475669853</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>61.43841586042542</v>
+        <v>9.983742577319131</v>
       </c>
       <c r="D6" t="n">
-        <v>62.06795403528024</v>
+        <v>10.08604253073304</v>
       </c>
       <c r="E6" t="n">
-        <v>8.302310750264049</v>
+        <v>1.349125496917908</v>
       </c>
       <c r="F6" t="n">
-        <v>9.274827542583708</v>
+        <v>1.507159475669853</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>66.18798325723212</v>
+        <v>10.75554727930022</v>
       </c>
       <c r="D7" t="n">
-        <v>66.76669224701605</v>
+        <v>10.84958749014011</v>
       </c>
       <c r="E7" t="n">
-        <v>8.302310750264049</v>
+        <v>1.349125496917908</v>
       </c>
       <c r="F7" t="n">
-        <v>9.274827542583708</v>
+        <v>1.507159475669853</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>49.16644603798057</v>
+        <v>7.989547481171843</v>
       </c>
       <c r="D8" t="n">
-        <v>49.07772952374172</v>
+        <v>7.975131047608029</v>
       </c>
       <c r="E8" t="n">
-        <v>8.302310750264049</v>
+        <v>1.349125496917908</v>
       </c>
       <c r="F8" t="n">
-        <v>9.274827542583708</v>
+        <v>1.507159475669853</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>46.86658623122832</v>
+        <v>7.615820262574602</v>
       </c>
       <c r="D9" t="n">
-        <v>46.53090867073202</v>
+        <v>7.561272658993953</v>
       </c>
       <c r="E9" t="n">
-        <v>8.302310750264049</v>
+        <v>1.349125496917908</v>
       </c>
       <c r="F9" t="n">
-        <v>9.274827542583708</v>
+        <v>1.507159475669853</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>66.45940258034261</v>
+        <v>10.79965291930568</v>
       </c>
       <c r="D10" t="n">
-        <v>65.58849369289187</v>
+        <v>10.65813022509493</v>
       </c>
       <c r="E10" t="n">
-        <v>8.302310750264049</v>
+        <v>1.349125496917908</v>
       </c>
       <c r="F10" t="n">
-        <v>9.274827542583708</v>
+        <v>1.507159475669853</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
